--- a/outputs_xlsx_solution/test33.4-wide-NF-1.xlsx
+++ b/outputs_xlsx_solution/test33.4-wide-NF-1.xlsx
@@ -113,6 +113,9 @@
     <t>fld F22, 0(X2)</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fld F20, 0(X1)</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -1230,6 +1236,9 @@
       <c r="Q13" t="s">
         <v>21</v>
       </c>
+      <c r="U13" t="s">
+        <v>26</v>
+      </c>
       <c r="V13" t="s">
         <v>8</v>
       </c>
@@ -1408,7 +1417,7 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U19" t="s">
         <v>5</v>
@@ -1437,7 +1446,7 @@
         <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V20" t="s">
         <v>5</v>
@@ -1447,6 +1456,9 @@
       </c>
       <c r="X20" t="s">
         <v>21</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>26</v>
       </c>
       <c r="Z20" t="s">
         <v>8</v>
@@ -1472,7 +1484,7 @@
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W21" t="s">
         <v>5</v>
@@ -1504,7 +1516,7 @@
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X22" t="s">
         <v>5</v>
@@ -1530,7 +1542,7 @@
         <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y23" t="s">
         <v>5</v>
@@ -1556,7 +1568,7 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z24" t="s">
         <v>5</v>
@@ -1585,7 +1597,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD25" t="s">
         <v>5</v>
@@ -1611,7 +1623,7 @@
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE26" t="s">
         <v>5</v>
@@ -1646,7 +1658,7 @@
         <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF27" t="s">
         <v>5</v>
@@ -1678,7 +1690,7 @@
         <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG28" t="s">
         <v>5</v>
@@ -1704,7 +1716,7 @@
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AH29" t="s">
         <v>5</v>
@@ -1730,7 +1742,7 @@
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AI30" t="s">
         <v>5</v>
@@ -1759,7 +1771,7 @@
         <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ31" t="s">
         <v>5</v>
@@ -1785,7 +1797,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK32" t="s">
         <v>5</v>
@@ -1820,7 +1832,7 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL33" t="s">
         <v>5</v>
@@ -1852,7 +1864,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM34" t="s">
         <v>5</v>
@@ -1878,7 +1890,7 @@
         <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AN35" t="s">
         <v>5</v>
@@ -1904,7 +1916,7 @@
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AO36" t="s">
         <v>5</v>
@@ -1933,7 +1945,7 @@
         <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS37" t="s">
         <v>5</v>
@@ -1962,7 +1974,7 @@
         <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AT38" t="s">
         <v>5</v>
@@ -1994,7 +2006,7 @@
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AU39" t="s">
         <v>5</v>
@@ -2020,7 +2032,7 @@
         <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AV40" t="s">
         <v>5</v>
@@ -2115,6 +2127,9 @@
       <c r="BA43" t="s">
         <v>21</v>
       </c>
+      <c r="BE43" t="s">
+        <v>26</v>
+      </c>
       <c r="BF43" t="s">
         <v>8</v>
       </c>
@@ -2293,7 +2308,7 @@
         <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE49" t="s">
         <v>5</v>
@@ -2322,7 +2337,7 @@
         <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF50" t="s">
         <v>5</v>
@@ -2332,6 +2347,9 @@
       </c>
       <c r="BH50" t="s">
         <v>21</v>
+      </c>
+      <c r="BI50" t="s">
+        <v>26</v>
       </c>
       <c r="BJ50" t="s">
         <v>8</v>
@@ -2357,7 +2375,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG51" t="s">
         <v>5</v>
@@ -2389,7 +2407,7 @@
         <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH52" t="s">
         <v>5</v>
@@ -2415,7 +2433,7 @@
         <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BI53" t="s">
         <v>5</v>
@@ -2441,7 +2459,7 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BJ54" t="s">
         <v>5</v>
@@ -2470,7 +2488,7 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BK55" t="s">
         <v>5</v>
@@ -2496,7 +2514,7 @@
         <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BL56" t="s">
         <v>5</v>
@@ -2531,7 +2549,7 @@
         <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BM57" t="s">
         <v>5</v>
@@ -2563,7 +2581,7 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BN58" t="s">
         <v>5</v>
@@ -2589,7 +2607,7 @@
         <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BO59" t="s">
         <v>5</v>
@@ -2618,7 +2636,7 @@
         <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BP60" t="s">
         <v>5</v>
@@ -2647,7 +2665,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ61" t="s">
         <v>5</v>
@@ -2673,7 +2691,7 @@
         <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BR62" t="s">
         <v>5</v>
@@ -2708,7 +2726,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS63" t="s">
         <v>5</v>
@@ -2740,7 +2758,7 @@
         <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BT64" t="s">
         <v>5</v>
@@ -2766,7 +2784,7 @@
         <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BU65" t="s">
         <v>5</v>
@@ -2792,7 +2810,7 @@
         <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BV66" t="s">
         <v>5</v>
@@ -2821,7 +2839,7 @@
         <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BZ67" t="s">
         <v>5</v>
@@ -2850,7 +2868,7 @@
         <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CA68" t="s">
         <v>5</v>
@@ -2882,7 +2900,7 @@
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CB69" t="s">
         <v>5</v>
@@ -2908,7 +2926,7 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CC70" t="s">
         <v>5</v>
@@ -3006,6 +3024,9 @@
       <c r="CH73" t="s">
         <v>21</v>
       </c>
+      <c r="CL73" t="s">
+        <v>26</v>
+      </c>
       <c r="CM73" t="s">
         <v>8</v>
       </c>
@@ -3184,7 +3205,7 @@
         <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CL79" t="s">
         <v>5</v>
@@ -3213,7 +3234,7 @@
         <v>72</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CM80" t="s">
         <v>5</v>
@@ -3223,6 +3244,9 @@
       </c>
       <c r="CO80" t="s">
         <v>21</v>
+      </c>
+      <c r="CP80" t="s">
+        <v>26</v>
       </c>
       <c r="CQ80" t="s">
         <v>8</v>
@@ -3248,7 +3272,7 @@
         <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CN81" t="s">
         <v>5</v>
@@ -3280,7 +3304,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CO82" t="s">
         <v>5</v>
@@ -3306,7 +3330,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CP83" t="s">
         <v>5</v>
@@ -3332,7 +3356,7 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CQ84" t="s">
         <v>5</v>
@@ -3361,7 +3385,7 @@
         <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CR85" t="s">
         <v>5</v>
@@ -3387,7 +3411,7 @@
         <v>72</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CS86" t="s">
         <v>5</v>
@@ -3422,7 +3446,7 @@
         <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CT87" t="s">
         <v>5</v>
@@ -3454,7 +3478,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CU88" t="s">
         <v>5</v>
@@ -3480,7 +3504,7 @@
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CV89" t="s">
         <v>5</v>
@@ -3509,7 +3533,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CW90" t="s">
         <v>5</v>
@@ -3538,7 +3562,7 @@
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CX91" t="s">
         <v>5</v>
@@ -3564,7 +3588,7 @@
         <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CY92" t="s">
         <v>5</v>
@@ -3599,7 +3623,7 @@
         <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CZ93" t="s">
         <v>5</v>
@@ -3631,7 +3655,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="DA94" t="s">
         <v>5</v>
@@ -3657,7 +3681,7 @@
         <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="DB95" t="s">
         <v>5</v>
@@ -3683,7 +3707,7 @@
         <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="DC96" t="s">
         <v>5</v>
@@ -3712,7 +3736,7 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DG97" t="s">
         <v>5</v>
@@ -3741,7 +3765,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DH98" t="s">
         <v>5</v>
@@ -3773,7 +3797,7 @@
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DI99" t="s">
         <v>5</v>
@@ -3799,7 +3823,7 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DJ100" t="s">
         <v>5</v>
@@ -3822,7 +3846,7 @@
         <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="DK101" t="s">
         <v>5</v>
@@ -3848,7 +3872,7 @@
         <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="DL102" t="s">
         <v>5</v>
@@ -3874,7 +3898,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="DM103" t="s">
         <v>5</v>
@@ -3897,7 +3921,7 @@
         <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="DN104" t="s">
         <v>5</v>
@@ -3920,7 +3944,7 @@
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="DO105" t="s">
         <v>5</v>
@@ -3943,7 +3967,7 @@
         <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DP106" t="s">
         <v>5</v>
@@ -3966,7 +3990,7 @@
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="DQ107" t="s">
         <v>5</v>
@@ -3989,7 +4013,7 @@
         <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="DR108" t="s">
         <v>5</v>
@@ -4012,7 +4036,7 @@
         <v>140</v>
       </c>
       <c r="C109" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="DS109" t="s">
         <v>5</v>
@@ -4029,7 +4053,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="112">
@@ -4037,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113">
@@ -4045,7 +4069,7 @@
         <v>6</v>
       </c>
       <c r="B113" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="114">
@@ -4053,7 +4077,7 @@
         <v>21</v>
       </c>
       <c r="B114" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="115">
@@ -4061,7 +4085,7 @@
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116">
@@ -4069,7 +4093,7 @@
         <v>10</v>
       </c>
       <c r="B116" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="117">
@@ -4077,23 +4101,39 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B118" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>55</v>
+      </c>
+      <c r="B119" t="s">
         <v>56</v>
       </c>
-      <c r="B119" t="s">
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
         <v>57</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>26</v>
+      </c>
+      <c r="B121" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
